--- a/skills/quotation/templates/询价模版.xlsx
+++ b/skills/quotation/templates/询价模版.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12960"/>
+    <workbookView windowWidth="29400" windowHeight="13040" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="报价表" sheetId="1" r:id="rId1"/>
-    <sheet name="上海UPS小货" sheetId="2" r:id="rId2"/>
-    <sheet name="空派小货（普货）" sheetId="3" r:id="rId3"/>
-    <sheet name="单位换算" sheetId="4" r:id="rId4"/>
+    <sheet name="报价表" sheetId="2" r:id="rId1"/>
+    <sheet name="上海UPS小货" sheetId="3" r:id="rId2"/>
+    <sheet name="空派小货（普货）" sheetId="4" r:id="rId3"/>
+    <sheet name="单位换算" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,8 +29,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
   <si>
     <t>需求</t>
   </si>
@@ -44,7 +66,24 @@
     <t>几色印刷</t>
   </si>
   <si>
-    <t>几个logo</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>logo</t>
+    </r>
   </si>
   <si>
     <t>SETUP FEE</t>
@@ -56,52 +95,299 @@
     <t>@Product_Name</t>
   </si>
   <si>
-    <t>客户需求量1</t>
-  </si>
-  <si>
-    <t>客户需求量2</t>
-  </si>
-  <si>
-    <t>客户需求量3</t>
-  </si>
-  <si>
-    <t>客户需求量4</t>
-  </si>
-  <si>
-    <t>客户需求量5</t>
-  </si>
-  <si>
-    <t>客户报价1</t>
-  </si>
-  <si>
-    <t>客户报价2</t>
-  </si>
-  <si>
-    <t>客户报价3</t>
-  </si>
-  <si>
-    <t>客户报价4</t>
-  </si>
-  <si>
-    <t>客户报价5</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户需求量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户需求量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户需求量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户需求量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户需求量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户报价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户报价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户报价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户报价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户报价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
   </si>
   <si>
     <t>产品</t>
   </si>
   <si>
-    <t>长(cm)</t>
-  </si>
-  <si>
-    <t>宽(cm)</t>
-  </si>
-  <si>
-    <t>高(cm)</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
   </si>
   <si>
     <t>公斤</t>
   </si>
   <si>
-    <t>件数/箱</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>件数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱</t>
+    </r>
   </si>
   <si>
     <t>单位重量</t>
@@ -110,25 +396,280 @@
     <t>单位体积</t>
   </si>
   <si>
-    <t>@箱子尺寸 长(cm)</t>
-  </si>
-  <si>
-    <t>@箱子尺寸 宽(cm)</t>
-  </si>
-  <si>
-    <t>@箱子尺寸 高(cm)</t>
-  </si>
-  <si>
-    <t>@重量(箱子+产品)公斤</t>
-  </si>
-  <si>
-    <t>@件数/箱</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱子尺寸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱子尺寸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱子尺寸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(cm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公斤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>件数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箱</t>
+    </r>
   </si>
   <si>
     <t>采购</t>
   </si>
   <si>
-    <t>产品采购单价¥</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品采购单价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>¥</t>
+    </r>
   </si>
   <si>
     <t>其他固定费用</t>
@@ -143,7 +684,51 @@
     <t>目标利润率</t>
   </si>
   <si>
-    <t>@1688价(元)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@1688</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>核价</t>
@@ -233,22 +818,124 @@
     <t>总报价</t>
   </si>
   <si>
-    <t>毛利1</t>
-  </si>
-  <si>
-    <t>毛利率1</t>
-  </si>
-  <si>
-    <t>毛利率2</t>
-  </si>
-  <si>
-    <t>毛利率3</t>
-  </si>
-  <si>
-    <t>毛利率4</t>
-  </si>
-  <si>
-    <t>毛利率5</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF262626"/>
+        <rFont val="Arial Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
   </si>
   <si>
     <t>体重倍数：
@@ -287,10 +974,7 @@
     <t>国家</t>
   </si>
   <si>
-    <t>美国</t>
-  </si>
-  <si>
-    <t>单价</t>
+    <t>运费单价</t>
   </si>
   <si>
     <t>深圳市中技物流义乌分公司</t>
@@ -305,7 +989,7 @@
     <t>重量KG</t>
   </si>
   <si>
-    <t>（空派小货）普货价格</t>
+    <t>（空派小货）普货单价</t>
   </si>
   <si>
     <t>注意事项：</t>
@@ -353,21 +1037,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="14">
+  <numFmts count="12">
     <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="General&quot; kg&quot;"/>
-    <numFmt numFmtId="180" formatCode="General&quot; g&quot;"/>
-    <numFmt numFmtId="181" formatCode="General&quot; cm³&quot;"/>
-    <numFmt numFmtId="182" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="183" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="184" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="General&quot; kg&quot;"/>
+    <numFmt numFmtId="179" formatCode="General&quot; g&quot;"/>
+    <numFmt numFmtId="180" formatCode="General&quot; cm³&quot;"/>
+    <numFmt numFmtId="181" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="48">
     <font>
@@ -407,42 +1089,61 @@
       <b/>
       <sz val="20"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="华文中宋"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="华文中宋"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="24"/>
@@ -458,22 +1159,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -544,19 +1238,6 @@
       <color rgb="FF000000"/>
       <name val="Arial Regular"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -702,6 +1383,12 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="MS Sans Serif"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="43">
     <fill>
@@ -724,7 +1411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,13 +1423,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFAAABD6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAABD6"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -957,139 +1644,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="16">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC0C0C0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC0C0C0"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC0C0C0"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC0C0C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1114,18 +1674,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1147,6 +1698,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1160,13 +1724,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1282,158 +1848,158 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="40" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="41" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="42" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1455,217 +2021,206 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="7" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="20" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="20" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="19" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="26" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="19" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1715,6 +2270,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规_Sheet1" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1986,829 +2542,815 @@
     <tabColor rgb="FFE97132"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S209"/>
+  <dimension ref="A1:S202"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2"/>
   <cols>
-    <col min="1" max="4" width="18.6923076923077" style="32" customWidth="1"/>
-    <col min="5" max="5" width="25.6442307692308" style="32" customWidth="1"/>
-    <col min="6" max="10" width="18.6923076923077" style="32" customWidth="1"/>
-    <col min="11" max="12" width="24" style="32" customWidth="1"/>
-    <col min="13" max="13" width="20" style="32" customWidth="1"/>
-    <col min="14" max="16" width="24" style="32" customWidth="1"/>
-    <col min="17" max="16384" width="14" style="32" customWidth="1"/>
+    <col min="1" max="4" width="18.6923076923077" style="25" customWidth="1"/>
+    <col min="5" max="5" width="25.6442307692308" style="25" customWidth="1"/>
+    <col min="6" max="10" width="18.6923076923077" style="25" customWidth="1"/>
+    <col min="11" max="12" width="24" style="25" customWidth="1"/>
+    <col min="13" max="13" width="20" style="25" customWidth="1"/>
+    <col min="14" max="16" width="24" style="25" customWidth="1"/>
+    <col min="17" max="20" width="14" style="25" customWidth="1"/>
+    <col min="21" max="16384" width="14" style="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:19">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:19">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="30">
         <v>1</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="30">
         <v>1</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="30">
         <f>IF(D2&gt;1,80,50)*E2</f>
         <v>50</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:19">
-      <c r="A3" s="36"/>
-      <c r="B3" s="34" t="s">
+      <c r="A3" s="29"/>
+      <c r="B3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="27" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:19">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:19">
-      <c r="A5" s="36"/>
-      <c r="B5" s="38">
+      <c r="A5" s="29"/>
+      <c r="B5" s="31">
         <f>$B$17*B4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="31">
         <f>$B$17*C4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="31">
         <f>$B$17*D4</f>
         <v>0</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="31">
         <f>$B$17*E4</f>
         <v>0</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="31">
         <f>$B$17*F4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:19">
-      <c r="A6" s="36"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="27" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:19">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:19">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="34" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:19">
-      <c r="A9" s="39"/>
-      <c r="B9" s="37" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="43">
-        <f>IFERROR(E9/F9*1000,0)</f>
+      <c r="G9" s="35">
+        <f>IFERROR(E9/F9*100,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="36">
         <f>IFERROR(B9*C9*D9/F9,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:19">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:19">
-      <c r="A11" s="39"/>
-      <c r="B11" s="37" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37">
+      <c r="C11" s="30"/>
+      <c r="D11" s="30">
         <v>1.1</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="37">
         <v>6.8</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="38">
         <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:19">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:19">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="42">
         <v>75</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="42">
         <v>65</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="43">
         <v>25</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53" t="s">
+      <c r="E13" s="44"/>
+      <c r="F13" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="44" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:19">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="45">
         <v>5000</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="45">
         <v>6000</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="46">
         <v>6000</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="57" t="b">
+      <c r="F14" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="57" t="b">
+      <c r="G14" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="57" t="b">
+      <c r="H14" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="58" t="s">
+      <c r="I14" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="S14" s="59"/>
+      <c r="S14" s="50"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:19">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="60">
+      <c r="B15" s="51">
         <v>0</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="51">
         <v>0</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="52">
         <v>0</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="63" t="str">
+      <c r="F15" s="54" t="str">
         <f>$B$2&amp;" "&amp;$C$2</f>
         <v>@Product_Number @Product_Name</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="63"/>
-      <c r="S15" s="59"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="54"/>
+      <c r="S15" s="50"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:19">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="31">
         <f>IFERROR($H9/B14,0)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="31">
         <f>IFERROR($H9/C14,0)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D16" s="56">
         <f>IFERROR($H9/D14,0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="66" t="str">
+      <c r="F16" s="57" t="str">
         <f>IF(B4&lt;&gt;"",B4&amp;" pcs","")</f>
         <v/>
       </c>
-      <c r="G16" s="66" t="str">
+      <c r="G16" s="57" t="str">
         <f>IF(C4&lt;&gt;"",C4&amp;" pcs","")</f>
         <v/>
       </c>
-      <c r="H16" s="66" t="str">
+      <c r="H16" s="57" t="str">
         <f>IF(D4&lt;&gt;"",D4&amp;" pcs","")</f>
         <v/>
       </c>
-      <c r="I16" s="67" t="str">
+      <c r="I16" s="58" t="str">
         <f>IF(E4&lt;&gt;"",E4&amp;" pcs","")</f>
         <v/>
       </c>
-      <c r="J16" s="66" t="str">
+      <c r="J16" s="57" t="str">
         <f>IF(F4&lt;&gt;"",F4&amp;" pcs","")</f>
         <v/>
       </c>
-      <c r="S16" s="59"/>
+      <c r="S16" s="50"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:14">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="31">
         <f>MAX(B16,$G9/1000)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="31">
         <f>MAX(C16,$G9/1000)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="56">
         <f>MAX(D16,$G9/1000)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="E17" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="68" t="str">
+      <c r="F17" s="59" t="str">
         <f>IF(B7&lt;&gt;"","$ "&amp;B7&amp;" /ea","")</f>
         <v/>
       </c>
-      <c r="G17" s="68" t="str">
+      <c r="G17" s="59" t="str">
         <f>IF(C7&lt;&gt;"","$ "&amp;C7&amp;" /ea","")</f>
         <v/>
       </c>
-      <c r="H17" s="68" t="str">
+      <c r="H17" s="59" t="str">
         <f>IF(D7&lt;&gt;"","$ "&amp;D7&amp;" /ea","")</f>
         <v/>
       </c>
-      <c r="I17" s="69" t="str">
+      <c r="I17" s="60" t="str">
         <f>IF(E7&lt;&gt;"","$ "&amp;E7&amp;" /ea","")</f>
         <v/>
       </c>
-      <c r="J17" s="68" t="str">
+      <c r="J17" s="59" t="str">
         <f>IF(F7&lt;&gt;"","$ "&amp;F7&amp;" /ea","")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:14">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="70">
-        <f>IFERROR(B16/($G9/1000),0)</f>
+      <c r="B18" s="61">
+        <f>IFERROR(B16/$G9,0)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="70">
-        <f>IFERROR(C16/($G9/1000),0)</f>
+      <c r="C18" s="61">
+        <f>IFERROR(C16/$G9,0)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="71">
-        <f>IFERROR(D16/($G9/1000),0)</f>
+      <c r="D18" s="62">
+        <f>IFERROR(D16/$G9,0)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="62" t="s">
+      <c r="E18" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="66" t="str">
+      <c r="F18" s="57" t="str">
         <f>IF(F2=0,"FREE","$ "&amp;$F2)&amp;" for "&amp;D2&amp;" C "&amp;E2&amp;" L"</f>
         <v>$ 50 for 1 C 1 L</v>
       </c>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="66"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:14">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="31">
         <f>ROUNDUP(B17*$B4,2)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="31">
         <f>ROUNDUP(C17*$B4,2)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="65">
+      <c r="D19" s="56">
         <f>MAX(ROUNDUP(D17*$B4,2),15)</f>
         <v>15</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="66" t="s">
+      <c r="F19" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="66"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:14">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="54" t="e">
+      <c r="B20" s="45" t="e">
         <f>B19/B4*B13/$E11*D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C20" s="54" t="e">
+      <c r="C20" s="45" t="e">
         <f>C19/B4*C13/$E11*D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D20" s="55" t="e">
+      <c r="D20" s="46" t="e">
         <f>D19/B4*D13/$E11*D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="62" t="str">
+      <c r="E20" s="53" t="str" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(F14,"Shipping Cost(Express):",G14,"Shipping Cost(Air):",H14,"Shipping Cost(Ocean):")</f>
         <v>Shipping Cost(Express):</v>
       </c>
-      <c r="F20" s="66" t="e">
+      <c r="F20" s="57" t="e" cm="1">
         <f t="array" ref="F20">_xlfn.IFS(F14,"$ "&amp;IF(B23=0,"FREE",B23)&amp;"/ea",G14,"$ "&amp;IF(C23=0,"FREE",C23)&amp;"/ea",H14,"$ "&amp;IF(D23=0,"FREE",D23)&amp;"/ea")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="66" t="str">
+      <c r="G20" s="57" t="str" cm="1">
         <f t="array" ref="G20">_xlfn.IFS(F14,"5-7 days via Express",G14,"12-15 days via Air",H14,"25-30 days via Ocean")</f>
         <v>5-7 days via Express</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="66"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:14">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="54" t="e">
+      <c r="B21" s="45" t="e">
         <f>B20+$B11*(1+B15)/$E11+($C11)/$B4/$E11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C21" s="54" t="e">
+      <c r="C21" s="45" t="e">
         <f>C20+$B11*(1+C15)/$E11+($C11)/$B4/$E11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D21" s="55" t="e">
+      <c r="D21" s="46" t="e">
         <f>D20+$B11*(1+D15)/$E11+($C11)/$B4/$E11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E21" s="62" t="str">
+      <c r="E21" s="53" t="str" cm="1">
         <f t="array" ref="E21">_xlfn.IFNA(_xlfn.IFS(AND(G14,F14),"Shipping Cost(Air)",AND(OR(F14,G14),H14),"Shipping Cost(Ocean)"),"")</f>
         <v>Shipping Cost(Air)</v>
       </c>
-      <c r="F21" s="66" t="e">
+      <c r="F21" s="57" t="e" cm="1">
         <f t="array" ref="F21">_xlfn.IFNA(_xlfn.IFS(AND(G14,F14),"$ "&amp;IF(C23=0,"FREE",C23)&amp;"/ea",AND(OR(F14,G14),H14),"$ "&amp;IF(D23=0,"FREE",D23)&amp;"/ea"),"")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="66" t="str">
+      <c r="G21" s="57" t="str" cm="1">
         <f t="array" ref="G21">_xlfn.IFNA(_xlfn.IFS(AND(G14,F14),"12-15 days via Air",AND(OR(F14,G14),H14),"25-30 days via Ocean"),"")</f>
         <v>12-15 days via Air</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="66"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:14">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="72" t="e">
+      <c r="B22" s="63" t="e">
         <f>ROUNDUP(B21/(1-$F11)-$B7,2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C22" s="72" t="e">
+      <c r="C22" s="63" t="e">
         <f>ROUNDUP(C21/(1-$F11)-$B7,2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D22" s="73" t="e">
+      <c r="D22" s="64" t="e">
         <f>ROUNDUP(D21/(1-$F11)-$B7,2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E22" s="62" t="str">
+      <c r="E22" s="53" t="str">
         <f>IF(AND(F14,G14,H14),"Shipping Cost(Ocean)","")</f>
         <v>Shipping Cost(Ocean)</v>
       </c>
-      <c r="F22" s="66" t="e">
+      <c r="F22" s="57" t="e">
         <f>IF(AND(F14,G14,H14),"$ "&amp;IF(D23=0,"FREE",D23)&amp;"/ea","")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="66" t="str">
+      <c r="G22" s="57" t="str">
         <f>IF(AND(F14,G14,H14),"25-30 days via Ocean","")</f>
         <v>25-30 days via Ocean</v>
       </c>
-      <c r="H22" s="66"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="66"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:14">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="74" t="e">
+      <c r="B23" s="65" t="e">
         <f>B22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C23" s="74" t="e">
+      <c r="C23" s="65" t="e">
         <f>C22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="75" t="e">
+      <c r="D23" s="66" t="e">
         <f>MAX(D22,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E23" s="62" t="str">
+      <c r="E23" s="53" t="str" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(F14,"Total Cost(Express):",G14,"Total Cost(Air):",H14,"Total Cost(Ocean):")</f>
         <v>Total Cost(Express):</v>
       </c>
-      <c r="F23" s="76" t="str">
+      <c r="F23" s="67" t="str">
         <f>IF(B4&lt;&gt;"",($B$23+B$7)*B$4,"")</f>
         <v/>
       </c>
-      <c r="G23" s="68" t="str">
+      <c r="G23" s="59" t="str">
         <f>IF(C4&lt;&gt;"",($B$23+C$7)*C$4,"")</f>
         <v/>
       </c>
-      <c r="H23" s="68" t="str">
+      <c r="H23" s="59" t="str">
         <f>IF(D4&lt;&gt;"",($B$23+D$7)*D$4,"")</f>
         <v/>
       </c>
-      <c r="I23" s="68" t="str">
+      <c r="I23" s="59" t="str">
         <f>IF(E4&lt;&gt;"",($B$23+E$7)*E$4,"")</f>
         <v/>
       </c>
-      <c r="J23" s="68" t="str">
+      <c r="J23" s="59" t="str">
         <f>IF(F4&lt;&gt;"",($B$23+F$7)*F$4,"")</f>
         <v/>
       </c>
-      <c r="K23" s="77"/>
-      <c r="N23" s="78"/>
+      <c r="K23" s="68"/>
+      <c r="N23" s="69"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:14">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="60">
+      <c r="B24" s="51">
         <f>IFERROR(B23/$B7,0)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="60">
+      <c r="C24" s="51">
         <f>IFERROR(C23/$B7,0)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="61">
+      <c r="D24" s="52">
         <f>IFERROR(D23/$B7,0)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="62" t="str">
+      <c r="E24" s="53" t="str" cm="1">
         <f t="array" ref="E24">_xlfn.IFNA(_xlfn.IFS(AND(G14,F14),"Total Cost(Air)",AND(OR(F14,G14),H14),"Total Cost(Ocean)"),"")</f>
         <v>Total Cost(Air)</v>
       </c>
-      <c r="F24" s="76" t="str">
+      <c r="F24" s="67" t="str">
         <f>IF(B4&lt;&gt;"",($C$23+B$7)*B$4,"")</f>
         <v/>
       </c>
-      <c r="G24" s="68" t="str">
+      <c r="G24" s="59" t="str">
         <f>IF(C4&lt;&gt;"",($C$23+C$7)*C$4,"")</f>
         <v/>
       </c>
-      <c r="H24" s="68" t="str">
+      <c r="H24" s="59" t="str">
         <f>IF(D4&lt;&gt;"",($C$23+D$7)*D$4,"")</f>
         <v/>
       </c>
-      <c r="I24" s="68" t="str">
+      <c r="I24" s="59" t="str">
         <f>IF(E4&lt;&gt;"",($C$23+E$7)*E$4,"")</f>
         <v/>
       </c>
-      <c r="J24" s="68" t="str">
+      <c r="J24" s="59" t="str">
         <f>IF(F4&lt;&gt;"",($C$23+F$7)*F$4,"")</f>
         <v/>
       </c>
-      <c r="N24" s="77"/>
+      <c r="N24" s="68"/>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:14">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="79" t="e">
+      <c r="B25" s="70" t="e">
         <f>B23+$B7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C25" s="79" t="e">
+      <c r="C25" s="70" t="e">
         <f>C23+$B7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D25" s="80" t="e">
+      <c r="D25" s="71" t="e">
         <f>D23+$B7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="62" t="str">
+      <c r="E25" s="53" t="str">
         <f>IF(AND(F14,G14,H14),"Total Cost(Ocean)","")</f>
         <v>Total Cost(Ocean)</v>
       </c>
-      <c r="F25" s="76" t="str">
+      <c r="F25" s="67" t="str">
         <f>IF(B4&lt;&gt;"",($D$23+B$7)*B$4,"")</f>
         <v/>
       </c>
-      <c r="G25" s="68" t="str">
+      <c r="G25" s="59" t="str">
         <f>IF(C4&lt;&gt;"",($D$23+C$7)*C$4,"")</f>
         <v/>
       </c>
-      <c r="H25" s="68" t="str">
+      <c r="H25" s="59" t="str">
         <f>IF(D4&lt;&gt;"",($D$23+D$7)*D$4,"")</f>
         <v/>
       </c>
-      <c r="I25" s="68" t="str">
+      <c r="I25" s="59" t="str">
         <f>IF(E4&lt;&gt;"",($D$23+E$7)*E$4,"")</f>
         <v/>
       </c>
-      <c r="J25" s="68" t="str">
+      <c r="J25" s="59" t="str">
         <f>IF(F4&lt;&gt;"",($D$23+F$7)*F$4,"")</f>
         <v/>
       </c>
-      <c r="N25" s="77"/>
+      <c r="N25" s="68"/>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:14">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="79" t="e">
+      <c r="B26" s="70" t="e">
         <f>(B23+$B7-B21)*$B4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C26" s="79" t="e">
+      <c r="C26" s="70" t="e">
         <f>(C23+$B7-C21)*$B4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D26" s="79" t="e">
+      <c r="D26" s="70" t="e">
         <f>(D23+$B7-D21)*$B4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N26" s="77"/>
+      <c r="N26" s="68"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:14">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="81" t="str">
+      <c r="B27" s="72" t="str">
         <f>IF($B4&lt;&gt;0,IFERROR((B23+$B7-B21)*$B4/(($B7+B23)*$B4),0),"")</f>
         <v/>
       </c>
-      <c r="C27" s="81" t="str">
+      <c r="C27" s="72" t="str">
         <f>IF($B4&lt;&gt;0,IFERROR((C23+$B7-C21)*$B4/(($B7+C23)*$B4),0),"")</f>
         <v/>
       </c>
-      <c r="D27" s="81" t="str">
+      <c r="D27" s="72" t="str">
         <f>IF($B4&lt;&gt;0,IFERROR((D23+$B7-D21)*$B4/(($B7+D23)*$B4),0),"")</f>
         <v/>
       </c>
-      <c r="N27" s="77"/>
+      <c r="N27" s="68"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:14">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="81" t="str">
+      <c r="B28" s="72" t="str">
         <f>IF($C4&lt;&gt;0,IFERROR((B23+$C7-B21)*$C4/(($C7+B23)*$C4),0),"")</f>
         <v/>
       </c>
-      <c r="C28" s="81" t="str">
+      <c r="C28" s="72" t="str">
         <f>IF($C4&lt;&gt;0,IFERROR((C23+$C7-C21)*$C4/(($C7+C23)*$C4),0),"")</f>
         <v/>
       </c>
-      <c r="D28" s="81" t="str">
+      <c r="D28" s="72" t="str">
         <f>IF($C4&lt;&gt;0,IFERROR((D23+$C7-D21)*$C4/(($C7+D23)*$C4),0),"")</f>
         <v/>
       </c>
-      <c r="N28" s="77"/>
+      <c r="N28" s="68"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:14">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="81" t="str">
+      <c r="B29" s="72" t="str">
         <f>IF($D4&lt;&gt;0,IFERROR((B23+$D7-B21)*$D4/(($D7+B23)*$D4),0),"")</f>
         <v/>
       </c>
-      <c r="C29" s="81" t="str">
+      <c r="C29" s="72" t="str">
         <f>IF($D4&lt;&gt;0,IFERROR((C23+$D7-C21)*$D4/(($D7+C23)*$D4),0),"")</f>
         <v/>
       </c>
-      <c r="D29" s="81" t="str">
+      <c r="D29" s="72" t="str">
         <f>IF($D4&lt;&gt;0,IFERROR((D23+$D7-D21)*$D4/(($D7+D23)*$D4),0),"")</f>
         <v/>
       </c>
-      <c r="N29" s="77"/>
+      <c r="N29" s="68"/>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:14">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="81" t="str">
+      <c r="B30" s="72" t="str">
         <f>IF($E4&lt;&gt;0,IFERROR((B23+$E7-B21)*$E4/(($E7+B23)*$E4),0),"")</f>
         <v/>
       </c>
-      <c r="C30" s="81" t="str">
+      <c r="C30" s="72" t="str">
         <f>IF($E4&lt;&gt;0,IFERROR((C23+$E7-C21)*$E4/(($E7+C23)*$E4),0),"")</f>
         <v/>
       </c>
-      <c r="D30" s="81" t="str">
+      <c r="D30" s="72" t="str">
         <f>IF($E4&lt;&gt;0,IFERROR((D23+$E7-D21)*$E4/(($E7+D23)*$E4),0),"")</f>
         <v/>
       </c>
-      <c r="N30" s="77"/>
+      <c r="N30" s="68"/>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:14">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="81" t="str">
+      <c r="B31" s="72" t="str">
         <f>IF($F4&lt;&gt;0,IFERROR((B23+$F7-B21)*$F4/(($F7+B23)*$F4),0),"")</f>
         <v/>
       </c>
-      <c r="C31" s="81" t="str">
+      <c r="C31" s="72" t="str">
         <f>IF($F4&lt;&gt;0,IFERROR((C23+$F7-C21)*$F4/(($F7+C23)*$F4),0),"")</f>
         <v/>
       </c>
-      <c r="D31" s="81" t="str">
+      <c r="D31" s="72" t="str">
         <f>IF($F4&lt;&gt;0,IFERROR((D23+$F7-D21)*$F4/(($F7+D23)*$F4),0),"")</f>
         <v/>
       </c>
-      <c r="N31" s="77"/>
-    </row>
-    <row r="32" ht="72" customHeight="1" spans="1:14">
-      <c r="A32" s="82" t="s">
+      <c r="N31" s="68"/>
+    </row>
+    <row r="32" ht="107" spans="1:14">
+      <c r="A32" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="82" t="s">
+      <c r="B32" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="82" t="s">
+      <c r="C32" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="82" t="s">
+      <c r="D32" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="82" t="s">
+      <c r="E32" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="F32" s="82" t="s">
+      <c r="F32" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="82" t="s">
+      <c r="G32" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="N32" s="77"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="1:14">
-      <c r="A33" s="83"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="N33" s="77"/>
-    </row>
-    <row r="34" ht="22" customHeight="1" spans="1:14">
-      <c r="N34" s="77"/>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:14">
-      <c r="N35" s="77"/>
-    </row>
+      <c r="N32" s="68"/>
+    </row>
+    <row r="33" ht="19" customHeight="1"/>
+    <row r="34" ht="19" customHeight="1"/>
+    <row r="35" ht="19" customHeight="1"/>
     <row r="36" ht="19" customHeight="1"/>
     <row r="37" ht="19" customHeight="1"/>
     <row r="38" ht="19" customHeight="1"/>
@@ -2976,26 +3518,12 @@
     <row r="200" ht="19" customHeight="1"/>
     <row r="201" ht="19" customHeight="1"/>
     <row r="202" ht="19" customHeight="1"/>
-    <row r="203" ht="19" customHeight="1"/>
-    <row r="204" ht="19" customHeight="1"/>
-    <row r="205" ht="19" customHeight="1"/>
-    <row r="206" ht="19" customHeight="1"/>
-    <row r="207" ht="19" customHeight="1"/>
-    <row r="208" ht="19" customHeight="1"/>
-    <row r="209" ht="19" customHeight="1"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="4">
     <mergeCell ref="E12:H12"/>
     <mergeCell ref="A1:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A33:A39"/>
-    <mergeCell ref="B33:B39"/>
-    <mergeCell ref="C33:C39"/>
-    <mergeCell ref="D33:D39"/>
-    <mergeCell ref="E33:E39"/>
-    <mergeCell ref="F33:F39"/>
-    <mergeCell ref="G33:G39"/>
   </mergeCells>
   <conditionalFormatting sqref="B18:D18">
     <cfRule type="iconSet" priority="5">
@@ -3013,6 +3541,31 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{43961235-efcc-403b-99d4-0f315ca3cb65}">
+            <x14:iconSet iconSet="3TrafficLights2" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>15</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B5:F5</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -3024,542 +3577,368 @@
   <dimension ref="A1:D200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="51" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" customWidth="1"/>
-    <col min="3" max="20" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="29.6442307692308" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="85" customHeight="1" spans="1:4">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:4">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="29" t="s">
+    </row>
+    <row r="3" ht="19" customHeight="1" spans="1:4">
+      <c r="A3" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="23">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1" spans="1:4">
+      <c r="A4" s="22">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:4">
+      <c r="A5" s="22">
+        <v>1.5</v>
+      </c>
+      <c r="B5" s="23">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:4">
+      <c r="A6" s="22">
+        <v>2</v>
+      </c>
+      <c r="B6" s="23">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:4">
+      <c r="A7" s="22">
+        <v>2.5</v>
+      </c>
+      <c r="B7" s="23">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:4">
+      <c r="A8" s="22">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:4">
+      <c r="A9" s="22">
+        <v>3.5</v>
+      </c>
+      <c r="B9" s="23">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:4">
+      <c r="A10" s="22">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:4">
+      <c r="A11" s="22">
+        <v>4.5</v>
+      </c>
+      <c r="B11" s="23">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:4">
+      <c r="A12" s="22">
+        <v>5</v>
+      </c>
+      <c r="B12" s="23">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:4">
+      <c r="A13" s="22">
+        <v>5.5</v>
+      </c>
+      <c r="B13" s="23">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:4">
+      <c r="A14" s="22">
+        <v>6</v>
+      </c>
+      <c r="B14" s="23">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:4">
+      <c r="A15" s="22">
+        <v>6.5</v>
+      </c>
+      <c r="B15" s="23">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:4">
+      <c r="A16" s="22">
+        <v>7</v>
+      </c>
+      <c r="B16" s="23">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:2">
+      <c r="A17" s="22">
+        <v>7.5</v>
+      </c>
+      <c r="B17" s="23">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:2">
+      <c r="A18" s="22">
+        <v>8</v>
+      </c>
+      <c r="B18" s="23">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:2">
+      <c r="A19" s="22">
+        <v>8.5</v>
+      </c>
+      <c r="B19" s="23">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:2">
+      <c r="A20" s="22">
+        <v>9</v>
+      </c>
+      <c r="B20" s="23">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:2">
+      <c r="A21" s="22">
+        <v>9.5</v>
+      </c>
+      <c r="B21" s="23">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:2">
+      <c r="A22" s="22">
+        <v>10</v>
+      </c>
+      <c r="B22" s="23">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:2">
+      <c r="A23" s="22">
+        <v>10.5</v>
+      </c>
+      <c r="B23" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:2">
+      <c r="A24" s="22">
+        <v>11</v>
+      </c>
+      <c r="B24" s="23">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:2">
+      <c r="A25" s="22">
+        <v>11.5</v>
+      </c>
+      <c r="B25" s="23">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:2">
+      <c r="A26" s="22">
+        <v>12</v>
+      </c>
+      <c r="B26" s="23">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:2">
+      <c r="A27" s="22">
+        <v>12.5</v>
+      </c>
+      <c r="B27" s="23">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:2">
+      <c r="A28" s="22">
+        <v>13</v>
+      </c>
+      <c r="B28" s="23">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1" spans="1:2">
+      <c r="A29" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="B29" s="23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:2">
+      <c r="A30" s="22">
+        <v>14</v>
+      </c>
+      <c r="B30" s="23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:2">
+      <c r="A31" s="22">
+        <v>14.5</v>
+      </c>
+      <c r="B31" s="23">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:2">
+      <c r="A32" s="22">
+        <v>15</v>
+      </c>
+      <c r="B32" s="23">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:2">
+      <c r="A33" s="22">
+        <v>15.5</v>
+      </c>
+      <c r="B33" s="23">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:2">
+      <c r="A34" s="22">
+        <v>16</v>
+      </c>
+      <c r="B34" s="23">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1" spans="1:2">
+      <c r="A35" s="22">
+        <v>16.5</v>
+      </c>
+      <c r="B35" s="23">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1" spans="1:2">
+      <c r="A36" s="22">
+        <v>17</v>
+      </c>
+      <c r="B36" s="23">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1" spans="1:2">
+      <c r="A37" s="22">
+        <v>17.5</v>
+      </c>
+      <c r="B37" s="23">
         <v>83</v>
       </c>
     </row>
-    <row r="3" ht="19" customHeight="1" spans="1:4">
-      <c r="A3" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="B3" s="31">
-        <v>160</v>
-      </c>
-      <c r="C3" s="29">
-        <f t="shared" ref="C3:C45" si="0">ROUND(B3/A3,0)</f>
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" ht="19" customHeight="1" spans="1:4">
-      <c r="A4" s="30">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31">
-        <v>210</v>
-      </c>
-      <c r="C4" s="29">
-        <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1" spans="1:4">
-      <c r="A5" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="B5" s="31">
-        <v>180</v>
-      </c>
-      <c r="C5" s="29">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:4">
-      <c r="A6" s="30">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31">
-        <v>210</v>
-      </c>
-      <c r="C6" s="29">
-        <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:4">
-      <c r="A7" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="B7" s="31">
-        <v>240</v>
-      </c>
-      <c r="C7" s="29">
-        <f t="shared" si="0"/>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:4">
-      <c r="A8" s="30">
-        <v>2</v>
-      </c>
-      <c r="B8" s="31">
-        <v>250</v>
-      </c>
-      <c r="C8" s="29">
-        <f t="shared" si="0"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:4">
-      <c r="A9" s="30">
-        <v>2.5</v>
-      </c>
-      <c r="B9" s="31">
-        <v>260</v>
-      </c>
-      <c r="C9" s="29">
-        <f t="shared" si="0"/>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:4">
-      <c r="A10" s="30">
-        <v>3</v>
-      </c>
-      <c r="B10" s="31">
-        <v>290</v>
-      </c>
-      <c r="C10" s="29">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:4">
-      <c r="A11" s="30">
-        <v>3.5</v>
-      </c>
-      <c r="B11" s="31">
-        <v>320</v>
-      </c>
-      <c r="C11" s="29">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:4">
-      <c r="A12" s="30">
-        <v>4</v>
-      </c>
-      <c r="B12" s="31">
-        <v>360</v>
-      </c>
-      <c r="C12" s="29">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:4">
-      <c r="A13" s="30">
-        <v>4.5</v>
-      </c>
-      <c r="B13" s="31">
-        <v>380</v>
-      </c>
-      <c r="C13" s="29">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:4">
-      <c r="A14" s="30">
-        <v>5</v>
-      </c>
-      <c r="B14" s="31">
-        <v>390</v>
-      </c>
-      <c r="C14" s="29">
-        <f t="shared" si="0"/>
+    <row r="38" ht="19" customHeight="1" spans="1:2">
+      <c r="A38" s="22">
+        <v>18</v>
+      </c>
+      <c r="B38" s="23">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1" spans="1:2">
+      <c r="A39" s="22">
+        <v>18.5</v>
+      </c>
+      <c r="B39" s="23">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1" spans="1:2">
+      <c r="A40" s="22">
+        <v>19</v>
+      </c>
+      <c r="B40" s="23">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1" spans="1:2">
+      <c r="A41" s="22">
+        <v>19.5</v>
+      </c>
+      <c r="B41" s="23">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1" spans="1:2">
+      <c r="A42" s="22">
+        <v>20</v>
+      </c>
+      <c r="B42" s="23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1" spans="1:2">
+      <c r="A43" s="22">
+        <v>20.5</v>
+      </c>
+      <c r="B43" s="23">
         <v>78</v>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1" spans="1:4">
-      <c r="A15" s="30">
-        <v>5.5</v>
-      </c>
-      <c r="B15" s="31">
-        <v>420</v>
-      </c>
-      <c r="C15" s="29">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1" spans="1:4">
-      <c r="A16" s="30">
-        <v>6</v>
-      </c>
-      <c r="B16" s="31">
-        <v>440</v>
-      </c>
-      <c r="C16" s="29">
-        <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1" spans="1:3">
-      <c r="A17" s="30">
-        <v>6.5</v>
-      </c>
-      <c r="B17" s="31">
-        <v>470</v>
-      </c>
-      <c r="C17" s="29">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:3">
-      <c r="A18" s="30">
-        <v>7</v>
-      </c>
-      <c r="B18" s="31">
-        <v>490</v>
-      </c>
-      <c r="C18" s="29">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1" spans="1:3">
-      <c r="A19" s="30">
-        <v>7.5</v>
-      </c>
-      <c r="B19" s="31">
-        <v>510</v>
-      </c>
-      <c r="C19" s="29">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1" spans="1:3">
-      <c r="A20" s="30">
-        <v>8</v>
-      </c>
-      <c r="B20" s="31">
-        <v>530</v>
-      </c>
-      <c r="C20" s="29">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1" spans="1:3">
-      <c r="A21" s="30">
-        <v>8.5</v>
-      </c>
-      <c r="B21" s="31">
-        <v>550</v>
-      </c>
-      <c r="C21" s="29">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="1:3">
-      <c r="A22" s="30">
-        <v>9</v>
-      </c>
-      <c r="B22" s="31">
-        <v>570</v>
-      </c>
-      <c r="C22" s="29">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1" spans="1:3">
-      <c r="A23" s="30">
-        <v>9.5</v>
-      </c>
-      <c r="B23" s="31">
-        <v>590</v>
-      </c>
-      <c r="C23" s="29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1" spans="1:3">
-      <c r="A24" s="30">
-        <v>10</v>
-      </c>
-      <c r="B24" s="31">
-        <v>620</v>
-      </c>
-      <c r="C24" s="29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1" spans="1:3">
-      <c r="A25" s="30">
-        <v>10.5</v>
-      </c>
-      <c r="B25" s="31">
-        <v>650</v>
-      </c>
-      <c r="C25" s="29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1" spans="1:3">
-      <c r="A26" s="30">
-        <v>11</v>
-      </c>
-      <c r="B26" s="31">
-        <v>680</v>
-      </c>
-      <c r="C26" s="29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1" spans="1:3">
-      <c r="A27" s="30">
-        <v>11.5</v>
-      </c>
-      <c r="B27" s="31">
-        <v>710</v>
-      </c>
-      <c r="C27" s="29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1" spans="1:3">
-      <c r="A28" s="30">
-        <v>12</v>
-      </c>
-      <c r="B28" s="31">
-        <v>730</v>
-      </c>
-      <c r="C28" s="29">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" ht="19" customHeight="1" spans="1:3">
-      <c r="A29" s="30">
-        <v>12.5</v>
-      </c>
-      <c r="B29" s="31">
-        <v>750</v>
-      </c>
-      <c r="C29" s="29">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1" spans="1:3">
-      <c r="A30" s="30">
-        <v>13</v>
-      </c>
-      <c r="B30" s="31">
-        <v>770</v>
-      </c>
-      <c r="C30" s="29">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1" spans="1:3">
-      <c r="A31" s="30">
-        <v>13.5</v>
-      </c>
-      <c r="B31" s="31">
-        <v>790</v>
-      </c>
-      <c r="C31" s="29">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1" spans="1:3">
-      <c r="A32" s="30">
-        <v>14</v>
-      </c>
-      <c r="B32" s="31">
-        <v>840</v>
-      </c>
-      <c r="C32" s="29">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1" spans="1:3">
-      <c r="A33" s="30">
-        <v>14.5</v>
-      </c>
-      <c r="B33" s="31">
-        <v>880</v>
-      </c>
-      <c r="C33" s="29">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1" spans="1:3">
-      <c r="A34" s="30">
-        <v>15</v>
-      </c>
-      <c r="B34" s="31">
-        <v>900</v>
-      </c>
-      <c r="C34" s="29">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1" spans="1:3">
-      <c r="A35" s="30">
-        <v>15.5</v>
-      </c>
-      <c r="B35" s="31">
-        <v>930</v>
-      </c>
-      <c r="C35" s="29">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1" spans="1:3">
-      <c r="A36" s="30">
-        <v>16</v>
-      </c>
-      <c r="B36" s="31">
-        <v>950</v>
-      </c>
-      <c r="C36" s="29">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" ht="19" customHeight="1" spans="1:3">
-      <c r="A37" s="30">
-        <v>16.5</v>
-      </c>
-      <c r="B37" s="31">
-        <v>980</v>
-      </c>
-      <c r="C37" s="29">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1" spans="1:3">
-      <c r="A38" s="30">
-        <v>17</v>
-      </c>
-      <c r="B38" s="31">
-        <v>990</v>
-      </c>
-      <c r="C38" s="29">
-        <f t="shared" si="0"/>
+    <row r="44" ht="19" customHeight="1" spans="1:2">
+      <c r="A44" s="24">
+        <v>20</v>
+      </c>
+      <c r="B44" s="23">
         <v>58</v>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1" spans="1:3">
-      <c r="A39" s="30">
-        <v>17.5</v>
-      </c>
-      <c r="B39" s="31">
-        <v>1030</v>
-      </c>
-      <c r="C39" s="29">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1" spans="1:3">
-      <c r="A40" s="30">
-        <v>18</v>
-      </c>
-      <c r="B40" s="31">
-        <v>1050</v>
-      </c>
-      <c r="C40" s="29">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1" spans="1:3">
-      <c r="A41" s="30">
-        <v>18.5</v>
-      </c>
-      <c r="B41" s="31">
-        <v>1070</v>
-      </c>
-      <c r="C41" s="29">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" ht="19" customHeight="1" spans="1:3">
-      <c r="A42" s="30">
-        <v>19</v>
-      </c>
-      <c r="B42" s="31">
-        <v>1080</v>
-      </c>
-      <c r="C42" s="29">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1" spans="1:3">
-      <c r="A43" s="30">
-        <v>19.5</v>
-      </c>
-      <c r="B43" s="31">
-        <v>1110</v>
-      </c>
-      <c r="C43" s="29">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1" spans="1:3">
-      <c r="A44" s="30">
-        <v>20</v>
-      </c>
-      <c r="B44" s="31">
-        <v>1150</v>
-      </c>
-      <c r="C44" s="29">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1" spans="1:3">
-      <c r="A45" s="30">
+    <row r="45" ht="19" customHeight="1" spans="1:2">
+      <c r="A45" s="24">
         <v>20.5</v>
       </c>
-      <c r="B45" s="31">
-        <v>1180</v>
-      </c>
-      <c r="C45" s="29">
-        <f t="shared" si="0"/>
+      <c r="B45" s="23">
         <v>58</v>
       </c>
     </row>
@@ -3735,427 +4114,371 @@
   <dimension ref="A1:H200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="20" width="12" style="1" customWidth="1"/>
+    <col min="1" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" ht="62" customHeight="1" spans="1:8">
+      <c r="A2" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" ht="62" customHeight="1" spans="1:8">
-      <c r="A2" s="10" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" ht="71" customHeight="1" spans="1:8">
+      <c r="A3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" ht="71" customHeight="1" spans="1:8">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:8">
+      <c r="A4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:8">
-      <c r="A4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:8">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15">
+        <v>114</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="6" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:8">
+      <c r="A6" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="B6" s="15">
+        <v>112</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:8">
+      <c r="A7" s="14">
+        <v>4</v>
+      </c>
+      <c r="B7" s="15">
+        <v>110</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:8">
+      <c r="A8" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="B8" s="15">
+        <v>107</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:8">
+      <c r="A9" s="14">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15">
+        <v>106</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:8">
+      <c r="A10" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="B10" s="15">
+        <v>99</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:8">
+      <c r="A11" s="14">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15">
+        <v>95</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:8">
+      <c r="A12" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="B12" s="15">
+        <v>91</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:8">
+      <c r="A13" s="14">
+        <v>7</v>
+      </c>
+      <c r="B13" s="15">
+        <v>90</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:8">
+      <c r="A14" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="B14" s="15">
+        <v>87</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:8">
+      <c r="A15" s="14">
+        <v>8</v>
+      </c>
+      <c r="B15" s="15">
+        <v>85</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:8">
+      <c r="A16" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="B16" s="15">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" ht="19" customHeight="1" spans="1:8">
-      <c r="A5" s="17">
-        <v>3</v>
-      </c>
-      <c r="B5" s="18">
-        <v>290</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="6">
-        <f t="shared" ref="H5:H28" si="0">ROUNDUP(B5/A5,0)</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:8">
-      <c r="A6" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="B6" s="18">
-        <v>330</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="6">
-        <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:8">
-      <c r="A7" s="17">
-        <v>4</v>
-      </c>
-      <c r="B7" s="18">
-        <v>340</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="6">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:8">
-      <c r="A8" s="17">
-        <v>4.5</v>
-      </c>
-      <c r="B8" s="18">
-        <v>360</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="6">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:8">
-      <c r="A9" s="17">
-        <v>5</v>
-      </c>
-      <c r="B9" s="18">
-        <v>390</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="6">
-        <f t="shared" si="0"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:7">
+      <c r="A17" s="14">
+        <v>9</v>
+      </c>
+      <c r="B17" s="15">
+        <v>82</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:7">
+      <c r="A18" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="B18" s="15">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:8">
-      <c r="A10" s="17">
-        <v>5.5</v>
-      </c>
-      <c r="B10" s="18">
-        <v>420</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="6">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:8">
-      <c r="A11" s="17">
-        <v>6</v>
-      </c>
-      <c r="B11" s="18">
-        <v>450</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="6">
-        <f t="shared" si="0"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:7">
+      <c r="A19" s="14">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15">
+        <v>76</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:7">
+      <c r="A20" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="B20" s="15">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:8">
-      <c r="A12" s="17">
-        <v>6.5</v>
-      </c>
-      <c r="B12" s="18">
-        <v>480</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="6">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:8">
-      <c r="A13" s="17">
-        <v>7</v>
-      </c>
-      <c r="B13" s="18">
-        <v>510</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="6">
-        <f t="shared" si="0"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:7">
+      <c r="A21" s="14">
+        <v>11</v>
+      </c>
+      <c r="B21" s="15">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:8">
-      <c r="A14" s="17">
-        <v>7.5</v>
-      </c>
-      <c r="B14" s="18">
-        <v>530</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="6">
-        <f t="shared" si="0"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:7">
+      <c r="A22" s="14">
+        <v>11.5</v>
+      </c>
+      <c r="B22" s="15">
+        <v>72</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:7">
+      <c r="A23" s="14">
+        <v>12</v>
+      </c>
+      <c r="B23" s="15">
         <v>71</v>
       </c>
-    </row>
-    <row r="15" ht="19" customHeight="1" spans="1:8">
-      <c r="A15" s="17">
-        <v>8</v>
-      </c>
-      <c r="B15" s="18">
-        <v>540</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="6">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1" spans="1:8">
-      <c r="A16" s="17">
-        <v>8.5</v>
-      </c>
-      <c r="B16" s="18">
-        <v>570</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="6">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1" spans="1:8">
-      <c r="A17" s="17">
-        <v>9</v>
-      </c>
-      <c r="B17" s="18">
-        <v>590</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="6">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:8">
-      <c r="A18" s="17">
-        <v>9.5</v>
-      </c>
-      <c r="B18" s="18">
-        <v>630</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="6">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1" spans="1:8">
-      <c r="A19" s="17">
-        <v>10</v>
-      </c>
-      <c r="B19" s="18">
-        <v>650</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="6">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1" spans="1:8">
-      <c r="A20" s="17">
-        <v>10.5</v>
-      </c>
-      <c r="B20" s="18">
-        <v>680</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="6">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1" spans="1:8">
-      <c r="A21" s="17">
-        <v>11</v>
-      </c>
-      <c r="B21" s="18">
-        <v>700</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="6">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="1:8">
-      <c r="A22" s="17">
-        <v>11.5</v>
-      </c>
-      <c r="B22" s="18">
-        <v>730</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="6">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1" spans="1:8">
-      <c r="A23" s="17">
-        <v>12</v>
-      </c>
-      <c r="B23" s="18">
-        <v>740</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="6">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1" spans="1:8">
-      <c r="A24" s="17">
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:7">
+      <c r="A24" s="14">
         <v>12.5</v>
       </c>
-      <c r="B24" s="18">
-        <v>760</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="6">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1" spans="1:8">
-      <c r="A25" s="17">
+      <c r="B24" s="15">
+        <v>72</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:7">
+      <c r="A25" s="14">
         <v>13</v>
       </c>
-      <c r="B25" s="18">
-        <v>780</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="6">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1" spans="1:8">
-      <c r="A26" s="17">
+      <c r="B25" s="15">
+        <v>71</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:7">
+      <c r="A26" s="14">
         <v>13.5</v>
       </c>
-      <c r="B26" s="18">
-        <v>800</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="6">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1" spans="1:8">
-      <c r="A27" s="17">
+      <c r="B26" s="15">
+        <v>71</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:7">
+      <c r="A27" s="14">
         <v>14</v>
       </c>
-      <c r="B27" s="18">
-        <v>820</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="6">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1" spans="1:8">
-      <c r="A28" s="17">
+      <c r="B27" s="15">
+        <v>70</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:7">
+      <c r="A28" s="14">
         <v>14.5</v>
       </c>
-      <c r="B28" s="18">
-        <v>850</v>
-      </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="6">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
+      <c r="B28" s="15">
+        <v>69</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" ht="19" customHeight="1"/>
     <row r="30" ht="19" customHeight="1"/>
@@ -4350,124 +4673,124 @@
   <dimension ref="A1:H200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="20" width="14" style="1" customWidth="1"/>
+    <col min="1" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="8" width="14" customWidth="1"/>
+    <col min="9" max="11" width="15" customWidth="1"/>
+    <col min="12" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1"/>
     <row r="2" ht="21" customHeight="1" spans="1:8">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="2" t="s">
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:8">
+      <c r="B3" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.51</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5.12</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2.49</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:8">
+      <c r="B4" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:8">
-      <c r="B3" s="3">
-        <v>2.25</v>
-      </c>
-      <c r="C3" s="3">
-        <v>5.51</v>
-      </c>
-      <c r="D3" s="3">
-        <v>5.12</v>
-      </c>
-      <c r="F3" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2.49</v>
-      </c>
-      <c r="H3" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:8">
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:8">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <f>B3*2.54</f>
         <v>5.715</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <f>C3*2.54</f>
         <v>13.9954</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <f>D3*2.54</f>
         <v>13.0048</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <f>F3/2.54</f>
         <v>2.16535433070866</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <f>G3/2.54</f>
         <v>0.980314960629921</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <f>H3/2.54</f>
         <v>7.8740157480315</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:8">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>100</v>
+      <c r="A7" s="1"/>
+      <c r="B7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="7">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6">
         <f>B5*C5*D5/5000</f>
         <v>0.20803443296256</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f>F3*G3*H3/5000</f>
         <v>0.05478</v>
       </c>
@@ -4475,35 +4798,35 @@
     <row r="9" ht="19" customHeight="1"/>
     <row r="10" ht="19" customHeight="1"/>
     <row r="11" ht="19" customHeight="1" spans="1:8">
-      <c r="B11" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:8">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>9.9</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>1.08</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:8">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>101</v>
+      <c r="C13" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:8">
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <f>ROUNDUP(B12*0.45359237,2)</f>
         <v>4.5</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <f>ROUNDUP(C12/0.45359237,2)</f>
         <v>2.39</v>
       </c>
